--- a/Reference Files/rag_salesbot-main/Capstone_Final.xlsx
+++ b/Reference Files/rag_salesbot-main/Capstone_Final.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0B7D799-5750-406D-9741-BD1F0DE9D69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16569031-086C-4B1B-AEB7-AB875A1AA186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conversational" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="250">
   <si>
     <t>Q.no</t>
   </si>
@@ -969,6 +969,9 @@
   </si>
   <si>
     <t>golden_SQL</t>
+  </si>
+  <si>
+    <t>Expected Rows</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -2370,9 +2373,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2394,6 +2394,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3121,14 +3124,14 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="18.75">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
@@ -3646,57 +3649,57 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="57.75">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>0.25</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="57.75">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <v>0.3</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="72.75">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>0.2</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="87">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>0.1</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="87">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>0.15</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>181</v>
       </c>
     </row>
@@ -3707,218 +3710,297 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02976571-79F9-4D82-AA2D-FD090E9AD97D}">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3" ht="15.75">
+      <c r="A1" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="308.25">
-      <c r="A2" s="9" t="s">
+      <c r="C1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="246.75">
+      <c r="A2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="339">
-      <c r="A3" s="9" t="s">
+      <c r="B2" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="277.5">
+      <c r="A3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="277.5">
-      <c r="A4" s="9" t="s">
+      <c r="B3" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="215.25">
+      <c r="A4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="215.25">
-      <c r="A5" s="9" t="s">
+      <c r="B4" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="169.5">
+      <c r="A5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="323.25">
-      <c r="A6" s="9" t="s">
+      <c r="B5" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="277.5">
+      <c r="A6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="277.5">
-      <c r="A7" s="9" t="s">
+      <c r="B6" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="215.25">
+      <c r="A7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="231">
-      <c r="A8" s="9" t="s">
+      <c r="B7" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="184.5">
+      <c r="A8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="184.5">
-      <c r="A9" s="9" t="s">
+      <c r="B8" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="138.75">
+      <c r="A9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="246.75">
-      <c r="A10" s="9" t="s">
+      <c r="B9" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="215.25">
+      <c r="A10" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="200.25">
-      <c r="A11" s="9" t="s">
+      <c r="B10" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="153.75">
+      <c r="A11" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="323.25">
-      <c r="A12" s="9" t="s">
+      <c r="B11" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="246.75">
+      <c r="A12" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="308.25">
-      <c r="A13" s="9" t="s">
+      <c r="B12" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="215.25">
+      <c r="A13" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="215.25">
-      <c r="A14" s="9" t="s">
+      <c r="B13" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="184.5">
+      <c r="A14" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="369">
-      <c r="A15" s="9" t="s">
+      <c r="B14" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="277.5">
+      <c r="A15" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="246.75">
-      <c r="A16" s="9" t="s">
+      <c r="B15" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="200.25">
+      <c r="A16" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="369">
-      <c r="A17" s="9" t="s">
+      <c r="B16" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="292.5">
+      <c r="A17" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="323.25">
-      <c r="A18" s="9" t="s">
+      <c r="B17" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="246.75">
+      <c r="A18" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="384">
-      <c r="A19" s="9" t="s">
+      <c r="B18" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="292.5">
+      <c r="A19" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="353.25">
-      <c r="A20" s="9" t="s">
+      <c r="B19" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C19">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="277.5">
+      <c r="A20" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="409.6">
-      <c r="A21" s="9" t="s">
+      <c r="B20" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="399.75">
+      <c r="A21" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="409.6">
-      <c r="A22" s="9" t="s">
+      <c r="B21" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="409.6">
+      <c r="A22" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="409.6">
-      <c r="A23" s="9" t="s">
+      <c r="B22" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="409.6">
+      <c r="A23" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="339">
-      <c r="A24" s="9" t="s">
+      <c r="B23" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="261.75">
+      <c r="A24" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="339">
-      <c r="A25" s="9" t="s">
+      <c r="B24" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="409.6">
-      <c r="A26" s="9" t="s">
+      <c r="C24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="261.75">
+      <c r="A25" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="323.25">
+      <c r="A26" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>208</v>
+      <c r="B26" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C26">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3936,35 +4018,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="43.5">
-      <c r="A1" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>210</v>
       </c>
+      <c r="B1" s="6" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>212</v>
       </c>
+      <c r="B2" s="6" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="3" spans="1:2" ht="29.25">
-      <c r="A3" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>214</v>
       </c>
+      <c r="B3" s="6" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>216</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -3984,212 +4066,212 @@
       <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>217</v>
+      <c r="B1" s="10" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="409.6">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>218</v>
+      <c r="B2" s="12" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="409.6">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>219</v>
+      <c r="B3" s="12" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="409.6">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>220</v>
+      <c r="B4" s="12" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="409.6">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>221</v>
+      <c r="B5" s="12" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="409.6">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>222</v>
+      <c r="B6" s="12" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="409.6">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>223</v>
+      <c r="B7" s="12" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="409.6">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>224</v>
+      <c r="B8" s="12" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="409.6">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>225</v>
+      <c r="B9" s="12" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="409.6">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>226</v>
+      <c r="B10" s="12" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="409.6">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>227</v>
+      <c r="B11" s="12" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="409.6">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>228</v>
+      <c r="B12" s="12" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="409.6">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>229</v>
+      <c r="B13" s="12" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="409.6">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>230</v>
+      <c r="B14" s="12" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="409.6">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>231</v>
+      <c r="B15" s="12" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="409.6">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="13" t="s">
-        <v>232</v>
+      <c r="B16" s="12" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="409.6">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="13" t="s">
-        <v>233</v>
+      <c r="B17" s="12" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="409.6">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="13" t="s">
-        <v>234</v>
+      <c r="B18" s="12" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="409.6">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>235</v>
+      <c r="B19" s="12" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="409.6">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="13" t="s">
-        <v>236</v>
+      <c r="B20" s="12" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="409.6">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>237</v>
+      <c r="B21" s="12" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="409.6">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="13" t="s">
-        <v>238</v>
+      <c r="B22" s="12" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="409.6">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>239</v>
+      <c r="B23" s="12" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="409.6">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>240</v>
+      <c r="B24" s="12" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.6">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="13" t="s">
-        <v>241</v>
+      <c r="B25" s="12" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="409.6">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>242</v>
+      <c r="B26" s="12" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="B27" s="14"/>
+      <c r="B27" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4206,43 +4288,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="29.25">
-      <c r="A1" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>243</v>
+      <c r="A1" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="29.25">
-      <c r="A2" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>212</v>
       </c>
+      <c r="B2" s="6" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="3" spans="1:2" ht="43.5">
-      <c r="A3" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>245</v>
       </c>
+      <c r="B3" s="6" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="4" spans="1:2" ht="43.5">
-      <c r="A4" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>247</v>
       </c>
+      <c r="B4" s="6" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>248</v>
+      <c r="A5" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>

--- a/Reference Files/rag_salesbot-main/Capstone_Final.xlsx
+++ b/Reference Files/rag_salesbot-main/Capstone_Final.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16569031-086C-4B1B-AEB7-AB875A1AA186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4295D9D-35BF-4701-8780-81E07F41C77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conversational" sheetId="2" r:id="rId1"/>
@@ -1189,6 +1189,9 @@
     <t>Output</t>
   </si>
   <si>
+    <t>Expected Performance (ms)</t>
+  </si>
+  <si>
     <t>=== text_to_sql: Performance Metrics (full) ===
 {
   "generation": {
@@ -2255,9 +2258,6 @@
 GROUP BY sales_agent
 ORDER BY win_rate DESC;
 ```</t>
-  </si>
-  <si>
-    <t>Generated SQL is syntactically correct and schema-aligned</t>
   </si>
   <si>
     <t>Time OK</t>
@@ -4056,221 +4056,379 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11D73018-6C74-4C78-8EC1-3ACE54906D78}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="55.140625" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="409.6">
+      <c r="C1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="409.6">
       <c r="A2" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.6">
+        <v>220</v>
+      </c>
+      <c r="C2">
+        <v>3000</v>
+      </c>
+      <c r="D2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="409.6">
       <c r="A3" s="11" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.6">
+        <v>221</v>
+      </c>
+      <c r="C3">
+        <v>4000</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="409.6">
       <c r="A4" s="11" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="409.6">
+        <v>222</v>
+      </c>
+      <c r="C4">
+        <v>2500</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="409.6">
       <c r="A5" s="11" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="409.6">
+        <v>223</v>
+      </c>
+      <c r="C5">
+        <v>3500</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="409.6">
       <c r="A6" s="11" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="409.6">
+        <v>224</v>
+      </c>
+      <c r="C6">
+        <v>4500</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="409.6">
       <c r="A7" s="11" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="409.6">
+        <v>225</v>
+      </c>
+      <c r="C7">
+        <v>2500</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="409.6">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="409.6">
+        <v>226</v>
+      </c>
+      <c r="C8">
+        <v>4000</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="409.6">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="409.6">
+        <v>227</v>
+      </c>
+      <c r="C9">
+        <v>3500</v>
+      </c>
+      <c r="D9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="409.6">
       <c r="A10" s="11" t="s">
         <v>31</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="409.6">
+        <v>228</v>
+      </c>
+      <c r="C10">
+        <v>3000</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="409.6">
       <c r="A11" s="11" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="409.6">
+        <v>229</v>
+      </c>
+      <c r="C11">
+        <v>3500</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="409.6">
       <c r="A12" s="11" t="s">
         <v>36</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="409.6">
+        <v>230</v>
+      </c>
+      <c r="C12">
+        <v>2000</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="409.6">
       <c r="A13" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="409.6">
+        <v>231</v>
+      </c>
+      <c r="C13">
+        <v>3000</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="409.6">
       <c r="A14" s="11" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="409.6">
+        <v>232</v>
+      </c>
+      <c r="C14">
+        <v>3500</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="409.6">
       <c r="A15" s="11" t="s">
         <v>43</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="409.6">
+        <v>233</v>
+      </c>
+      <c r="C15">
+        <v>3500</v>
+      </c>
+      <c r="D15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="409.6">
       <c r="A16" s="11" t="s">
         <v>46</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="409.6">
+        <v>234</v>
+      </c>
+      <c r="C16">
+        <v>2500</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="409.6">
       <c r="A17" s="11" t="s">
         <v>48</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="409.6">
+        <v>235</v>
+      </c>
+      <c r="C17">
+        <v>4500</v>
+      </c>
+      <c r="D17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="409.6">
       <c r="A18" s="11" t="s">
         <v>51</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="409.6">
+        <v>236</v>
+      </c>
+      <c r="C18">
+        <v>3000</v>
+      </c>
+      <c r="D18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="409.6">
       <c r="A19" s="11" t="s">
         <v>54</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="409.6">
+        <v>237</v>
+      </c>
+      <c r="C19">
+        <v>3500</v>
+      </c>
+      <c r="D19">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="409.6">
       <c r="A20" s="11" t="s">
         <v>56</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="409.6">
+        <v>238</v>
+      </c>
+      <c r="C20">
+        <v>6000</v>
+      </c>
+      <c r="D20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="409.6">
       <c r="A21" s="11" t="s">
         <v>58</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="409.6">
+        <v>239</v>
+      </c>
+      <c r="C21">
+        <v>3500</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="409.6">
       <c r="A22" s="11" t="s">
         <v>61</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="409.6">
+        <v>240</v>
+      </c>
+      <c r="C22">
+        <v>3500</v>
+      </c>
+      <c r="D22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="409.6">
       <c r="A23" s="11" t="s">
         <v>64</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="409.6">
+        <v>241</v>
+      </c>
+      <c r="C23">
+        <v>3500</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="409.6">
       <c r="A24" s="11" t="s">
         <v>66</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="409.6">
+        <v>242</v>
+      </c>
+      <c r="C24">
+        <v>3000</v>
+      </c>
+      <c r="D24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="409.6">
       <c r="A25" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="409.6">
+        <v>243</v>
+      </c>
+      <c r="C25">
+        <v>3000</v>
+      </c>
+      <c r="D25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="409.6">
       <c r="A26" s="11" t="s">
         <v>71</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>244</v>
+      </c>
+      <c r="C26">
+        <v>3000</v>
+      </c>
+      <c r="D26">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="B27" s="13"/>
     </row>
   </sheetData>
@@ -4280,7 +4438,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69CFAAEF-C20E-4B42-9325-282F863838F8}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -4289,41 +4447,33 @@
   <sheetData>
     <row r="1" spans="1:2" ht="29.25">
       <c r="A1" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="29.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="43.5">
       <c r="A2" s="6" t="s">
-        <v>212</v>
+        <v>245</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="43.5">
       <c r="A3" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="43.5">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="6" t="s">
-        <v>247</v>
+        <v>216</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="B5" s="6" t="s">
         <v>249</v>
       </c>
     </row>

--- a/Reference Files/rag_salesbot-main/Capstone_Final.xlsx
+++ b/Reference Files/rag_salesbot-main/Capstone_Final.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4295D9D-35BF-4701-8780-81E07F41C77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4569BA90-3D65-493C-B6FB-F05B3D696B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conversational" sheetId="2" r:id="rId1"/>
@@ -36,9 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="250">
-  <si>
-    <t>Q.no</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="176">
+  <si>
+    <t>ID</t>
   </si>
   <si>
     <t>Question</t>
@@ -50,928 +50,253 @@
     <t>Evaluation Purpose</t>
   </si>
   <si>
-    <t>Expected Output</t>
-  </si>
-  <si>
-    <t>AI Answer</t>
-  </si>
-  <si>
-    <t>Evaluation Metric</t>
-  </si>
-  <si>
-    <t>Score(1-5)</t>
+    <t>Expected Elements</t>
+  </si>
+  <si>
+    <t>I have availability in my schedule, can you provide me with 3 recommendations for who to contact and why?</t>
+  </si>
+  <si>
+    <t>Recommendation / Decision Support</t>
+  </si>
+  <si>
+    <t>Evaluate the agent’s ability to recommend accounts to contact based on CRM signals and provide reasoning.</t>
+  </si>
+  <si>
+    <t>Which accounts should I prioritize this week to maximize potential revenue?</t>
+  </si>
+  <si>
+    <t>Test prioritization based on deal value, opportunity stage, and account signals.</t>
+  </si>
+  <si>
+    <t>Which deals appear most promising right now and why?</t>
+  </si>
+  <si>
+    <t>Opportunity Recommendation</t>
+  </si>
+  <si>
+    <t>Evaluate reasoning ability when identifying promising opportunities.</t>
+  </si>
+  <si>
+    <t>Which deals should I focus on closing this quarter?</t>
+  </si>
+  <si>
+    <t>Recommendation / Sales Strategy</t>
+  </si>
+  <si>
+    <t>Test prioritization logic based on deal value and stage.</t>
+  </si>
+  <si>
+    <t>Which accounts might require proactive outreach soon?</t>
+  </si>
+  <si>
+    <t>Recommendation</t>
+  </si>
+  <si>
+    <t>Evaluate predictive reasoning about upcoming sales engagement.</t>
+  </si>
+  <si>
+    <t>Based on current data, what sales strategy would you recommend for the next month?</t>
+  </si>
+  <si>
+    <t>Strategic Recommendation</t>
+  </si>
+  <si>
+    <t>Evaluate higher-level reasoning and strategy generation from CRM data.</t>
+  </si>
+  <si>
+    <t>Are there any meetings, tasks, or open engagements that I should follow-up on?</t>
+  </si>
+  <si>
+    <t>Follow-up Detection</t>
+  </si>
+  <si>
+    <t>Evaluate the agent’s ability to detect pending meetings, tasks, or opportunities requiring follow-up.</t>
+  </si>
+  <si>
+    <t>Which accounts have not been contacted recently but have active opportunities?</t>
+  </si>
+  <si>
+    <t>Evaluate the system’s ability to detect neglected opportunities.</t>
+  </si>
+  <si>
+    <t>Are there any deals that appear to be stalled in the pipeline?</t>
+  </si>
+  <si>
+    <t>Pipeline Analysis</t>
+  </si>
+  <si>
+    <t>Test the agent’s ability to identify opportunities that have not progressed.</t>
+  </si>
+  <si>
+    <t>Which accounts should receive follow-up before the end of the quarter?</t>
+  </si>
+  <si>
+    <t>Test ability to identify time-sensitive engagement opportunities.</t>
+  </si>
+  <si>
+    <t>Which opportunities have not progressed recently and may require attention?</t>
+  </si>
+  <si>
+    <t>Pipeline Monitoring</t>
+  </si>
+  <si>
+    <t>Evaluate detection of stagnating deals.</t>
+  </si>
+  <si>
+    <t>Can you provide me with a summary of previous interactions with Yearin?</t>
+  </si>
+  <si>
+    <t>Interaction Summarization</t>
+  </si>
+  <si>
+    <t>Evaluate the agent’s ability to summarize historical interaction records accurately and concisely.</t>
+  </si>
+  <si>
+    <t>Summarize the recent sales activity for Account Yearin.</t>
+  </si>
+  <si>
+    <t>Evaluate the ability to synthesize interaction history into a concise narrative.</t>
+  </si>
+  <si>
+    <t>Provide a short overview of our relationship with Account Yearin.</t>
+  </si>
+  <si>
+    <t>Account Relationship Summary</t>
+  </si>
+  <si>
+    <t>Test the agent’s ability to summarize overall engagement history.</t>
+  </si>
+  <si>
+    <t>What are the key takeaways from recent interactions with Account Yearin?</t>
+  </si>
+  <si>
+    <t>Evaluate the agent’s ability to extract important insights from interaction logs.</t>
+  </si>
+  <si>
+    <t>Provide a brief summary of the last three interactions with Account Yearin.</t>
+  </si>
+  <si>
+    <t>Test summarization accuracy and grounding in interaction data.</t>
+  </si>
+  <si>
+    <t>What is the current status of the opportunities associated with Account Yearin?</t>
+  </si>
+  <si>
+    <t>Opportunity Status Analysis</t>
+  </si>
+  <si>
+    <t>Evaluate the agent’s ability to summarize pipeline information.</t>
+  </si>
+  <si>
+    <t>Which customers have high propensity to buy but limited recent engagement?</t>
+  </si>
+  <si>
+    <t>Opportunity Identification</t>
+  </si>
+  <si>
+    <t>Test whether the agent can identify high-potential accounts that may need outreach.</t>
+  </si>
+  <si>
+    <t>Which accounts have frequent interactions but no closed deals yet?</t>
+  </si>
+  <si>
+    <t>Analytical Insight</t>
+  </si>
+  <si>
+    <t>Evaluate ability to identify engagement patterns that may indicate sales inefficiencies.</t>
+  </si>
+  <si>
+    <t>Which sectors appear to generate the most successful deals?</t>
+  </si>
+  <si>
+    <t>Business Insight Generation</t>
+  </si>
+  <si>
+    <t>Evaluate ability to extract insights from sector performance.</t>
+  </si>
+  <si>
+    <t>What insights can you provide about recent sales activity across the pipeline?</t>
+  </si>
+  <si>
+    <t>Evaluate the system’s ability to generate meaningful sales insights.</t>
+  </si>
+  <si>
+    <t>Which accounts show strong engagement but low conversion rates?</t>
+  </si>
+  <si>
+    <t>Evaluate ability to identify patterns between engagement and deal outcomes.</t>
+  </si>
+  <si>
+    <t>Which sales activities appear to be most effective based on recent data?</t>
+  </si>
+  <si>
+    <t>Sales Effectiveness Analysis</t>
+  </si>
+  <si>
+    <t>Evaluate ability to identify successful sales behaviors.</t>
+  </si>
+  <si>
+    <t>What patterns do you observe among recently won deals?</t>
+  </si>
+  <si>
+    <t>Evaluate ability to detect patterns in successful deals.</t>
+  </si>
+  <si>
+    <t>Which accounts should I prepare for upcoming meetings with?</t>
+  </si>
+  <si>
+    <t>Meeting Preparation</t>
+  </si>
+  <si>
+    <t>Test ability to integrate meeting schedules with account context.</t>
+  </si>
+  <si>
+    <t>Dimension</t>
+  </si>
+  <si>
+    <t>Weights</t>
+  </si>
+  <si>
+    <t>Relevance</t>
+  </si>
+  <si>
+    <t>Directly addresses the question</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>Claims supported by CRM data</t>
+  </si>
+  <si>
+    <t>Completeness</t>
+  </si>
+  <si>
+    <t>Facts, reasoning, and next steps included</t>
+  </si>
+  <si>
+    <t>Actionability</t>
+  </si>
+  <si>
+    <t>Recommendations are prioritized and useful</t>
+  </si>
+  <si>
+    <t>Safety</t>
+  </si>
+  <si>
+    <t>No unsafe actions or fabricated data</t>
+  </si>
+  <si>
+    <t>question</t>
+  </si>
+  <si>
+    <t>golden_SQL</t>
+  </si>
+  <si>
+    <t>Expected Rows</t>
   </si>
   <si>
     <t>How many accounts exist in each office location?</t>
-  </si>
-  <si>
-    <t>Aggregation / Counting Questions</t>
-  </si>
-  <si>
-    <t>Test ability to count records grouped by a dimension (office location).</t>
-  </si>
-  <si>
-    <t>What are the top 5 accounts with the highest revenue per employee?</t>
-  </si>
-  <si>
-    <t>Ranking Questions</t>
-  </si>
-  <si>
-    <t>Test ranking logic and calculation of derived business metrics.</t>
-  </si>
-  <si>
-    <t>Which sectors have the highest average revenue?</t>
-  </si>
-  <si>
-    <t>Aggregation + Ranking query</t>
-  </si>
-  <si>
-    <t>Test AVG aggregation and ability to rank grouped results.</t>
-  </si>
-  <si>
-    <t>What are the 5 oldest companies in the database?</t>
-  </si>
-  <si>
-    <t>Temporal Ranking</t>
-  </si>
-  <si>
-    <t>Test ordering by date fields and retrieving oldest records.</t>
-  </si>
-  <si>
-    <t>Which accounts have both high revenue and high propensity to buy?</t>
-  </si>
-  <si>
-    <t>Filtering (Multi-condition)</t>
-  </si>
-  <si>
-    <t>Test conditional filtering with multiple business criteria.</t>
-  </si>
-  <si>
-    <t>How many accounts exist in each sector?</t>
-  </si>
-  <si>
-    <t>Aggregation / Group-by</t>
-  </si>
-  <si>
-    <t>Test grouping and counting across categorical attributes.</t>
-  </si>
-  <si>
-    <t>What are the top 5 accounts with highest propensity to buy?</t>
-  </si>
-  <si>
-    <t>Ranking</t>
-  </si>
-  <si>
-    <t>Test ranking using a predictive score column.</t>
-  </si>
-  <si>
-    <t>Which products are the most expensive?</t>
-  </si>
-  <si>
-    <t>Test ordering numeric values and retrieving highest entries.</t>
-  </si>
-  <si>
-    <t>How many products exist in each series?</t>
-  </si>
-  <si>
-    <t>Test grouping by product series and counting records.</t>
-  </si>
-  <si>
-    <t>What is the average price of products in each series?</t>
-  </si>
-  <si>
-    <t>Aggregation (AVG)</t>
-  </si>
-  <si>
-    <t>Test ability to compute averages across grouped categories.</t>
-  </si>
-  <si>
-    <t>How many sales opportunities exist in each deal stage?</t>
-  </si>
-  <si>
-    <t>Test counting records grouped by pipeline stage.</t>
-  </si>
-  <si>
-    <t>How many deals are in each deal stage?</t>
-  </si>
-  <si>
-    <t>Test pipeline distribution analysis using grouped counts.</t>
-  </si>
-  <si>
-    <t>What is the total value of all won deals?</t>
-  </si>
-  <si>
-    <t>Aggregation (SUM)</t>
-  </si>
-  <si>
-    <t>Test ability to compute total revenue for filtered records.</t>
-  </si>
-  <si>
-    <t>Which sales agents closed the most deals?</t>
-  </si>
-  <si>
-    <t>Aggregation + Ranking</t>
-  </si>
-  <si>
-    <t>Test counting deals per agent and ranking results.</t>
-  </si>
-  <si>
-    <t>What are the top 5 largest deals by value?</t>
-  </si>
-  <si>
-    <t>Test ordering deals by monetary value.</t>
-  </si>
-  <si>
-    <t>Which accounts generated the most revenue from won deals?</t>
-  </si>
-  <si>
-    <t>Join + Aggregation + Ranking</t>
-  </si>
-  <si>
-    <t>Test multi-table join and aggregation logic.</t>
-  </si>
-  <si>
-    <t>What is the average deal value for each sales agent?</t>
-  </si>
-  <si>
-    <t>Aggregation + Group-by</t>
-  </si>
-  <si>
-    <t>Test calculating averages across grouped sales agents.</t>
-  </si>
-  <si>
-    <t>Which sales agents generated the highest total revenue?</t>
-  </si>
-  <si>
-    <t>Test revenue aggregation and ranking agents.</t>
-  </si>
-  <si>
-    <t>Which product generated the most revenue?</t>
-  </si>
-  <si>
-    <t>Test joining deal and product tables and calculating revenue.</t>
-  </si>
-  <si>
-    <t>What is the total revenue generated per product series?</t>
-  </si>
-  <si>
-    <t>Join + Aggregation</t>
-  </si>
-  <si>
-    <t>Test hierarchical aggregation by product category.</t>
-  </si>
-  <si>
-    <t>Which sales manager generated the most revenue through their team?</t>
-  </si>
-  <si>
-    <t>Hierarchical Aggregation / Join</t>
-  </si>
-  <si>
-    <t>Test multi-level aggregation across manager–agent relationships.</t>
-  </si>
-  <si>
-    <t>Which regional office generated the most revenue?</t>
-  </si>
-  <si>
-    <t>Test revenue aggregation by geographic region.</t>
-  </si>
-  <si>
-    <t>Which accounts have the highest total interaction count?</t>
-  </si>
-  <si>
-    <t>Test counting interaction records per account.</t>
-  </si>
-  <si>
-    <t>Which accounts have won deals but no recorded interactions?</t>
-  </si>
-  <si>
-    <t>Join + Filtering (Negative condition)</t>
-  </si>
-  <si>
-    <t>Test ability to detect missing relationships using joins.</t>
-  </si>
-  <si>
-    <t>Which sales agents have the highest win rate?</t>
-  </si>
-  <si>
-    <t>Derived Metric + Aggregation</t>
-  </si>
-  <si>
-    <t>Test ratio calculations (wins / total deals).</t>
-  </si>
-  <si>
-    <t>Generative AI Evaluation Questions</t>
-  </si>
-  <si>
-    <t>Expected Elements</t>
-  </si>
-  <si>
-    <t>I have availability in my schedule, can you provide me with 3 recommendations for who to contact and why?</t>
-  </si>
-  <si>
-    <t>Recommendation / Decision Support</t>
-  </si>
-  <si>
-    <t>Evaluate the agent’s ability to recommend accounts to contact based on CRM signals and provide reasoning.</t>
-  </si>
-  <si>
-    <t>Based on your current outstanding work items, I recommend reaching out to the following contacts:
-Scott Ashley (Konmatfix)
-Reason: You've recently had a constructive Zoom meeting discussing the MG Special product. It's a good opportunity to follow up on any next steps that were outlined during your discussion. This can help maintain momentum and clarify any outstanding details.
-Elizabeth Peterson (Yearin)
-Reason: You've confirmed final details for a deal with Yearin, but there appears to be no further follow-ups recorded. It's essential to ensure they have no further questions or requirements before closing out this deal.
-These contacts should be prioritized as they relate to ongoing deals and communications, allowing you to efficiently utilize your schedule.</t>
-  </si>
-  <si>
-    <t>Which accounts should I prioritize this week to maximize potential revenue?</t>
-  </si>
-  <si>
-    <t>Test prioritization based on deal value, opportunity stage, and account signals.</t>
-  </si>
-  <si>
-    <t>To maximize potential revenue this week, you should prioritize the following accounts:
-Kan-code
-Potential Revenue: $11,698.03
-Additionally, you have the following outstanding work items that are currently in the "Engaging" stage:
-Konmatfix
-Product: MG Special
-Last Meeting: Completed on November 2, 2025
-Yearin
-Product: GTX Basic
-Last Meeting: Completed on September 3, 2025
-Focusing on Kan-code for its high potential revenue, along with following up on the engaging accounts Konmatfix and Yearin, will help optimize your efforts this week.</t>
-  </si>
-  <si>
-    <t>Which deals appear most promising right now and why?</t>
-  </si>
-  <si>
-    <t>Opportunity Recommendation</t>
-  </si>
-  <si>
-    <t>Evaluate reasoning ability when identifying promising opportunities.</t>
-  </si>
-  <si>
-    <t>It appears that there are currently no deals in the 'Engaging' stage that are expected to close within the next 30 days. This means there are no promising deals to highlight at this moment.
-If you'd like, I can help you with other inquiries or provide information about different types of deals.</t>
-  </si>
-  <si>
-    <t>Which deals should I focus on closing this quarter?</t>
-  </si>
-  <si>
-    <t>Recommendation / Sales Strategy</t>
-  </si>
-  <si>
-    <t>Test prioritization logic based on deal value and stage.</t>
-  </si>
-  <si>
-    <t>Here’s a summary of your outstanding work items as well as insights into potential deals to focus on closing this quarter:
-Outstanding Work Items:
-Konmatfix
-Stage: Engaging
-Product: MG Special
-Last Interaction: Meeting on November 2, 2025
-Notes: The meeting was constructive and focusing on cooperation moving forward.
-Yearin
-Stage: Engaging
-Product: GTX Basic
-Last Interaction: Meeting on September 3, 2025
-Notes: Confirmed final details during the call.
-Deals Closing This Quarter:
-Unfortunately, I did not find any specific deals in the pipeline that are closing within the next 30 days, which indicates that you may not have urgent deadlines this quarter based on current data.
-Recommendations:
-Focus on the Konmatfix and Yearin deals as they are currently in the engaging stage and would benefit from follow-up actions.
-Since there are no immediate closing deals, utilize this time to strengthen relationships and ensure these engagements are moving forward effectively.
-If you need any further assistance or strategies on these items, feel free to ask!</t>
-  </si>
-  <si>
-    <t>Which accounts might require proactive outreach soon?</t>
-  </si>
-  <si>
-    <t>Recommendation</t>
-  </si>
-  <si>
-    <t>Evaluate predictive reasoning about upcoming sales engagement.</t>
-  </si>
-  <si>
-    <t>Based on the analysis of outstanding work and the recent engagement history, here are the accounts that may require proactive outreach soon:
-Accounts with Recent Meetings:
-Konmatfix
-Last Contact: Meeting on November 2, 2025
-Product Involved: MG Special
-Status: Engaging
-Yearin
-Last Contact: Meeting on September 3, 2025
-Product Involved: GTX Basic
-Status: Engaging
-Additional Accounts Requiring Outreach:
-Acme Corporation
-Sector: Technology
-Revenue: $1,100.04
-Betasoloin
-Sector: Medical
-Revenue: $251.41
-Betatech
-Sector: Medical
-Revenue: $647.18
-Bioholding
-Sector: Medical
-Revenue: $587.34
-Bubba Gump
-Sector: Software
-Revenue: $987.39
-Cheers
-Sector: Entertainment
-Revenue: $4,269.90
-Codehow
-Sector: Software
-Revenue: $2,714.90
-Conecom
-Sector: Technology
-Revenue: $1,520.66
-The accounts listed above show varying levels of recent engagement and represent opportunities where proactive reach-out could help secure further engagement. The first two accounts, Konmatfix and Yearin, are already in the 'Engaging' stage and had more recent interactions compared to others, which suggests they could be good starting points for outreach efforts.</t>
-  </si>
-  <si>
-    <t>Based on current data, what sales strategy would you recommend for the next month?</t>
-  </si>
-  <si>
-    <t>Strategic Recommendation</t>
-  </si>
-  <si>
-    <t>Evaluate higher-level reasoning and strategy generation from CRM data.</t>
-  </si>
-  <si>
-    <t>Based on the latest data, here’s a recommended sales strategy for the upcoming month, taking into account your outstanding tasks and market conditions:
-Current Situation Assessment
-Outstanding Work Items:
-You have two projects currently in the "Engaging" stage:
-Konmatfix (Product: MG Special): You recently completed a productive meeting focusing on enhancing the integration of MG Advanced.
-Yearin (Product: GTX Basic): Involves finalizing details for a proposal, which requires timely follow-up to maintain momentum.
-Sales Trends &amp; Challenges:
-Top Products: Unfortunately, there was no data retrieved for the most popular products sold in the last month.
-Common Objections: The main objections revolve around concerns about integration compatibility and the clarity of transition timelines. Among the common issues shared were:
-Integration capabilities and flexibility of solutions.
-Concerns regarding operational continuity during implementation.
-Need for tailored examples and case studies to address client-specific scenarios.
-Recommended Strategy
-Focus on Client Engagement:
-Prioritize maintaining strong communication with current leads, particularly Konmatfix and Yearin. Schedule follow-ups to reinforce commitments demonstrated during meetings and ensure queries are answered promptly.
-Preparation for tailored next steps is critical. For Konmatfix, ensure that the technical integration plan is solidified and clearly documented.
-Addressing Objections Proactively:
-Create detailed documentation that clearly outlines integration processes and timelines. Prepare case studies that highlight past client successes to instill confidence in prospective customers facing compatibility concerns.
-Consider developing a FAQ document addressing these prevalent objections based on insights collected from prior interactions.
-Product Highlight Campaign:
-Even though specific sales data for products was not accessible, you can strategize on pushing the MG Special and GTX Basic as front-runners. Create promotional materials that convey their unique selling propositions, particularly how they solve current pain points around efficiency and integration.
-Supplement these promotions with workshops or demo sessions tailored for potential clients highlighting these products.
-Team Collaboration:
-Coordinate with your technical team to ensure that they are prepared to lead detailed technical discussions in upcoming meetings. This will help eradicate concerns regarding seamless transitions and operational disruptions.
-Continuous feedback loops with clients post-demonstrations will be crucial in fine-tuning your approach.
-Tracking Progress:
-Set specific outcome-based goals for the leads you are engaging with. Monitor the engagement levels and follow through on commitments made during discussions.
-Conclusion
-Focusing on strong client communication, addressing integration concerns proactively, promoting key product features, and ensuring team readiness for technical discussions will position you well in the upcoming month. Regularly reviewing the outcomes of your efforts will also enable you to adapt quickly if needed. Be sure to schedule your upcoming follow-ups and stay on top of any client queries or concerns to assure a smoother sales process.</t>
-  </si>
-  <si>
-    <t>Are there any meetings, tasks, or open engagements that I should follow-up on?</t>
-  </si>
-  <si>
-    <t>Follow-up Detection</t>
-  </si>
-  <si>
-    <t>Evaluate the agent’s ability to detect pending meetings, tasks, or opportunities requiring follow-up.</t>
-  </si>
-  <si>
-    <t>Currently, you have a couple of outstanding work items to follow up on:
-Open Engagements
-Konmatfix
-Last Meeting: November 2, 2025
-Product: MG Special
-Status: Engaging
-Details: You held a constructive Zoom meeting with Scott Ashley, discussing the integration of MG Advanced, addressing technical glitches, and ensuring minimal downtime. It’s important to follow up on the timeline for addressing technical hurdles and continuing discussions next week.
-Yearin
-Last Meeting: September 3, 2025
-Product: GTX Basic
-Status: Engaging
-Details: Following your call with Elizabeth Peterson, you confirmed details for a demonstration of the GTX Pro. Elizabeth is eager to see its scalability and integration capabilities. You agreed to send a follow-up email summarizing the demo points, and it's crucial to prepare the technical components and refine the demo scenarios for alignment with their needs.
-Follow-up Actions
-Konmatfix: Schedule the next meeting to evaluate progress on the technical issues and updates.
-Yearin: Send the follow-up email with the demo details and ensure your team is prepared for the presentation.
-These points should guide your immediate follow-up actions and ensure you're well-prepared for your engagements.</t>
-  </si>
-  <si>
-    <t>Which accounts have not been contacted recently but have active opportunities?</t>
-  </si>
-  <si>
-    <t>Evaluate the system’s ability to detect neglected opportunities.</t>
-  </si>
-  <si>
-    <t>Here are the accounts that have not been contacted recently (i.e., last contacted over 30 days ago) but have active opportunities:
-Groovestreet
-Iselectrics
-Labdrill
-Scotfind
-Y-corporation
-Doncon
-Dontechi
-Donware
-Initech
-Plexzap
-Konmatfix
-Bioplex
-Goodsilron
-Kan-code
-Donquadtech
-Funholding
-Hatfan
-Treequote
-Acme Corporation
-Bubba Gump
-Cheers
-Dalttechnology
-Faxquote
-Genco Pura Olive Oil Company
-Hottechi
-Rundofase
-Warephase
-Betasoloin
-Conecom
-Green-Plus
-Scottech
-Sonron
-Stanredtax
-Toughzap
-Ganjaflex
-Inity
-Isdom
-The New York Inquirer
-Zumgoity
-Cancity
-Dambase
-Gekko &amp; Co
-Nam-zim
-Statholdings
-Sumace
-Bluth Company
-Codehow
-Kinnamplus
-Betatech
-Domzoom
-Finhigh
-Konex
-Lexiqvolax
-Mathtouch
-Opentech
-Sunnamplex
-Yearin
-Zathunicon
-Bioholding
-Fasehatice
-Globex Corporation
-Gogozoom
-Ontomedia
-Plusstrip
-Plussunin
-Vehement Capital Partners
-Xx-holding
-Xx-zobam
-Newex
-Silis
-Singletechno
-Umbrella Corporation
-Zencorporation
-Zotware
-Blackzim
-Golddex
-Zoomit
-Finjob
-J-Texon
-Massive Dynamic
-Rangreen
-Rantouch
-Streethex
-Condax
-Ron-tech
-These accounts present potential opportunities for outreach to revive engagement.</t>
-  </si>
-  <si>
-    <t>Are there any deals that appear to be stalled in the pipeline?</t>
-  </si>
-  <si>
-    <t>Pipeline Analysis</t>
-  </si>
-  <si>
-    <t>Test the agent’s ability to identify opportunities that have not progressed.</t>
-  </si>
-  <si>
-    <t>There are currently 1589 deals that appear to be stalled in the pipeline. These deals are in the 'Engaging' stage but have not progressed or been updated in the last 30 days.
-Here's an overview of some highlighted accounts with stalled deals:
-Acme Corporation:
-5 GTX Plus Pro, Account Manager: Kami Bicknell, Engaged on: 2025-10-30
-Various other GTX products with different account managers (Zane Levy, Corliss Cosme, etc.)
-Betasoloin:
-Multiple MG Special, GTXPro, and GTX Plus Basic deals, engaged by various account managers.
-Betatech:
-MG Special and GTX Pro products also showing as stalled, with engagement dates around late 2025.
-Bioholding, Bubba Gump, Codehow, and others all have several stalled deals as well.
-If you would like detailed information about specific accounts or deals, please let me know!</t>
-  </si>
-  <si>
-    <t>Which accounts should receive follow-up before the end of the quarter?</t>
-  </si>
-  <si>
-    <t>Test ability to identify time-sensitive engagement opportunities.</t>
-  </si>
-  <si>
-    <t>Currently, you have two accounts that are in the "Engaging" stage and should receive follow-up before the end of the quarter:
-Konmatfix
-Last Activity: Completed meeting on November 2, 2025.
-Product: MG Special
-Yearin
-Last Activity: Completed meeting on September 3, 2025.
-Product: GTX Basic
-Both accounts are due for follow-up, especially given that there are no expected closings reported within the next month. Focus on reaching out to Konmatfix and Yearin to maintain momentum and encourage progression towards closing in your engagements.</t>
-  </si>
-  <si>
-    <t>Which opportunities have not progressed recently and may require attention?</t>
-  </si>
-  <si>
-    <t>Pipeline Monitoring</t>
-  </si>
-  <si>
-    <t>Evaluate detection of stagnating deals.</t>
-  </si>
-  <si>
-    <t>Here are the key opportunities that have not progressed recently and may require your attention:
-Konmatfix
-Status: Engaging
-Last Activity: Meeting completed on 2025-11-02
-Notes: Focus was on addressing integration issues; urgent troubleshooting sessions are needed with their IT department to resolve technical glitches that are hindering progress. Scott from Konmatfix expects detailed updates on these engagements next week.
-Yearin
-Status: Engaging
-Last Activity: Meeting completed on 2025-09-03
-Notes: During the last call, it was confirmed that a demonstration was pending, and Elizabeth expressed keen interest in seeing how the solution aligns with their infrastructure. Follow-ups are essential to confirm scheduling and readiness.
-Additionally, from queries on opportunities showing lack of recent progress that may require more immediate attention:
-Other Notable Opportunities (all in Engaging stage and with last activity older than approximately one month):
-Betatech: Last meeting in July, eager to finalize technical details for a product demo.
-Ganjaflex: Active dialogues have not moved past initial customization discussions since November.
-Zathunicon: Previous discussions were focused on integration, last completed call was in early November.
-These opportunities should be prioritized for follow-ups, ensuring that next steps are solidified and any potential technical bottlenecks are addressed swiftly. Consider scheduling check-in meetings or reaching out for updates as needed.</t>
-  </si>
-  <si>
-    <t>Can you provide me with a summary of previous interactions with Yearin?</t>
-  </si>
-  <si>
-    <t>Interaction Summarization</t>
-  </si>
-  <si>
-    <t>Evaluate the agent’s ability to summarize historical interaction records accurately and concisely.</t>
-  </si>
-  <si>
-    <t>Here's a summary of your previous interactions with Yearin, focusing on the key activities, discussions, and follow-ups related to your communication with Elizabeth Peterson:
-Email (Completed) - January 22, 2025
-You thanked Elizabeth for a detailed conversation about the GTX Pro. Emphasized the importance of scalability and integration with their existing infrastructure. Proposed a tailored demo session to address their operational challenges and align with their goals.
-Meeting (Scheduled) - February 12, 2025
-Discussed aligning schedules for the upcoming demo. Elizabeth expressed interest in how the GTX Pro could optimize operations and highlighted the need for clear demonstrations. The demo is set for next Tuesday, which will include her technical lead.
-Meeting (Scheduled) - April 27, 2025
-Confirmed demo details over Zoom. Elizabeth expected a focus on real-time data processing and differentiation from NorthPeak's offerings. You assured her that the demo would address these aspects and proposed including future product enhancements.
-Email (Scheduled) - July 12, 2025
-Reiterated anticipation for the upcoming demo, emphasizing tailored scenarios to highlight scalability and integration capabilities compared to NorthPeak. Requested input on any specific areas to cover during the presentation.
-Meeting (Completed) - September 3, 2025
-Confirmed final details for the demo, with Elizabeth eager to see how GTX Pro integrates with their systems. Requested specific scenarios for illustrating solutions to their challenges. Agreed to follow up with a summary to ensure alignment ahead of the demo.
-This series of interactions indicates a strong engagement with Yearin, focusing on addressing their specific needs and emphasizing the strategic fit of GTX Pro within their operations.</t>
-  </si>
-  <si>
-    <t>Summarize the recent sales activity for Account Yearin.</t>
-  </si>
-  <si>
-    <t>Evaluate the ability to synthesize interaction history into a concise narrative.</t>
-  </si>
-  <si>
-    <t>Here's a summary of the recent sales activity for the account "Yearin":
-Overview of Recent Sales Activity
-Account Details:
-Established: 2005
-Revenue: $2,261.05 million
-Employees: 3,851
-Location: United States
-Sales Progress Summary
-Closed Deals:
-Total Deals Won: 21
-Total Value of Won Deals: $18,427 (across various products)
-Key Wins:
-GTX Plus Pro - Significant focus on integration and scalability in real-time environments.
-GTX Basic and MG Advanced solutions tailored to specific needs.
-Engagements and Preparations for Demos:
-Ongoing communication with Elizabeth Peterson from Yearin, highlighting strategic collaboration and responsiveness to their operational challenges.
-Demos Discussed: Custom demonstrations to showcase GTX Pro’s integration capabilities tailored to Yearin's existing systems.
-Next Steps:
-Scheduled demos focusing on the specific needs identified during discussions.
-Key decision-makers, including technical leads, will be involved to enhance the engagement and ensure alignment with Yearin's objectives.
-Interaction Highlights:
-Meetings and Conversations:
-Detailed discussions took place regarding Yearin's operational needs and objectives for the GTPro's capabilities, emphasizing responses to competition from NorthPeak.
-Future product enhancements are proposed to align with Yearin’s strategic goals.
-Overall, Yearin's engagement has shown promising potential with several products already positioned favorably. The sales team continues to maintain proactive communication with key stakeholders ensuring that their needs are prioritized and addressed effectively.</t>
-  </si>
-  <si>
-    <t>Provide a short overview of our relationship with Account Yearin.</t>
-  </si>
-  <si>
-    <t>Account Relationship Summary</t>
-  </si>
-  <si>
-    <t>Test the agent’s ability to summarize overall engagement history.</t>
-  </si>
-  <si>
-    <t>Overview of Our Relationship with Account Yearin
-Account Details:
-Name: Yearin
-Sector: Retail
-Year Established: 2005
-Revenue: $2261.05 million
-Employees: 3851
-Location: United States
-Propensity to Buy: 0.642857
-Interactions:
-The key contact for Yearin is Elizabeth Peterson.
-Recent interactions include multiple meetings with completed statuses indicating strong engagement.
-Notable latest interaction took place on September 3, 2025, showcasing continuous communication.
-Sales Pipeline:
-Yearin has multiple deals associated with it, primarily in the retail products category, such as MG Advanced, GTX Basic, and MG Special.
-Several deals have been won; however, there are also instances of lost deals.
-Current Status:
-Yearin is currently categorized as Engaging.
-There are active works in progress associated with this account.
-Overall, Yearin presents a significant and established partnership with notable opportunities for continued sales engagements and upselling possibilities.</t>
-  </si>
-  <si>
-    <t>What are the key takeaways from recent interactions with Account Yearin?</t>
-  </si>
-  <si>
-    <t>Evaluate the agent’s ability to extract important insights from interaction logs.</t>
-  </si>
-  <si>
-    <t>ere are the key takeaways from recent interactions with Account Yearin, specifically focusing on communications with Elizabeth Peterson:
-Upcoming Demo Focus:
-Scheduled Demo: A demonstration of the GTX Pro is set for September 3, 2025. Elizabeth Peterson expressed enthusiasm about seeing how the solution aligns with Yearin's infrastructure.
-Key Validation Points: Elizabeth wants the demo to address specific scenarios showcasing the GTX Pro's scalability and integration capabilities, particularly in comparison to their current system challenges and NorthPeak's offerings.
-Preparation and Expectations:
-There have been multiple communications confirming demo details, including discussions on how to highlight the GTX Pro's strengths in real-time data processing and scalability.
-Elizabeth emphasized the need for clear distinctions between GTX Pro and NorthPeak, particularly concerning long-term adaptability.
-Engagement Strategy:
-The inclusion of Yearin's technical lead in the demo aims to facilitate deeper engagement with their IT team, addressing integration concerns and operational needs.
-Future enhancements of GTX Pro related to aligning with Yearin's strategic goals were proposed, fostering continued collaboration.
-Communication Overview:
-Several emails and meetings were exchanged, with the last email sent on July 12, emphasizing the planned demo's custom approach. Earlier meetings focused on aligning schedules and confirming expectations for the demonstration.
-In summary, the focus on tailoring the demo to Yearin's specific needs, addressing integration concerns, and differentiating from competitors are pivotal in solidifying a partnership with Yearin. Continuous engagement with key stakeholders reinforces our commitment to meeting their operational objectives.</t>
-  </si>
-  <si>
-    <t>Provide a brief summary of the last three interactions with Account Yearin.</t>
-  </si>
-  <si>
-    <t>Test summarization accuracy and grounding in interaction data.</t>
-  </si>
-  <si>
-    <t>Here is a brief summary of the last three interactions with Account Yearin:
-Meeting (Completed) - September 3, 2025: A call was held with Elizabeth Peterson to finalize details for an upcoming demonstration of the GTX Pro. Elizabeth expressed enthusiasm for the demo, particularly interested in how the solution can align with their infrastructure and its scalability. She requested that the demo include specific scenarios to illustrate problem-solving for their current system challenges. A follow-up email summarizing key points was agreed upon to ensure alignment.
-Email (Scheduled) - July 12, 2025: An email was sent to Elizabeth, outlining the preparation for the Tuesday demo. The email focused on how the GTX Pro would integrate with Yearin's systems and its superior scalability and real-time data processing capabilities compared to competitors. Elizabeth was encouraged to share any specific areas of interest for the demo to tailor the presentation to her needs.
-Meeting (Scheduled) - April 27, 2025: A Zoom meeting was held where Elizabeth confirmed the demo details and shared her team's expectations. She highlighted the need for the session to address integration and differentiate GTX Plus Pro from NorthPeak's offerings, especially regarding real-time data processing capabilities. The discussion emphasized preparing a tailored and impactful presentation.
-Overall, these interactions show a strong focus on aligning the demo with Yearin's specific needs and expectations, along with an emphasis on integration and differentiation from competitors.</t>
-  </si>
-  <si>
-    <t>What is the current status of the opportunities associated with Account Yearin?</t>
-  </si>
-  <si>
-    <t>Opportunity Status Analysis</t>
-  </si>
-  <si>
-    <t>Evaluate the agent’s ability to summarize pipeline information.</t>
-  </si>
-  <si>
-    <t>The current status of the opportunities associated with the Account Yearin is as follows:
-Opportunities Overview
-Won Opportunities (Total: 44)
-Multiple products under various deal stages have been successfully closed, with total amounts in the range of 55 to 6,117.
-A few notable wins:
-GTXPro products contributed significantly, with amounts of 5,558 and 5,316.
-Lost Opportunities (Total: 18)
-Several opportunities were lost across various products, mostly with amounts of $0.
-Notably, there were losses in MG Advanced and GTX Plus Pro products.
-Engaging Opportunities (Total: 3)
-There are currently three opportunities in the 'Engaging' stage:
-GTX Basic and MG Special products with no defined close dates yet.
-Prospecting Opportunities (Total: 3)
-Three opportunities are listed under 'Prospecting' stage for GTX Plus Basic, GTXPro, and MG Special, also with no defined close dates.
-Summary of Key Data Points
-Won Total Amount: Significant wins with amounts contributing to overall sales.
-Engagement Status: Active engagements with potential for future conversion.
-Prospecting Stage: Newly identified potentials, showing ongoing sales inputs.
-Overall, the account is performing well with a strong number of wins but also reflects some ongoing opportunities that need attention, particularly those in the engaging and prospecting stages.</t>
-  </si>
-  <si>
-    <t>Which customers have high propensity to buy but limited recent engagement?</t>
-  </si>
-  <si>
-    <t>Opportunity Identification</t>
-  </si>
-  <si>
-    <t>Test whether the agent can identify high-potential accounts that may need outreach.</t>
-  </si>
-  <si>
-    <t>Here are the customers with a high propensity to buy but limited recent engagement (last engagement over 3 months ago):
-Dalttechnology (Account ID: 1013)
-Donquadtech (Account ID: 1017)
-Finjob (Account ID: 1023)
-Gekko &amp; Co (Account ID: 1026)
-Goodsilron (Account ID: 1031)
-Newex (Account ID: 1050)
-Plusstrip (Account ID: 1054)
-Rangreen (Account ID: 1056)
-Zoomit (Account ID: 1082)
-These accounts are ideal targets for re-engagement efforts to convert their high buying potential into actual sales.</t>
-  </si>
-  <si>
-    <t>Which accounts have frequent interactions but no closed deals yet?</t>
-  </si>
-  <si>
-    <t>Analytical Insight</t>
-  </si>
-  <si>
-    <t>Evaluate ability to identify engagement patterns that may indicate sales inefficiencies.</t>
-  </si>
-  <si>
-    <t>There are currently no accounts with frequent interactions (more than 5 interactions in the last 3 months) but no closed deals. If you need help with anything else, feel free to ask!</t>
-  </si>
-  <si>
-    <t>Which sectors appear to generate the most successful deals?</t>
-  </si>
-  <si>
-    <t>Business Insight Generation</t>
-  </si>
-  <si>
-    <t>Evaluate ability to extract insights from sector performance.</t>
-  </si>
-  <si>
-    <t>The sectors that generate the most successful deals (Closed Won) are as follows:
-Retail: 799 deals
-Technology: 671 deals
-Medical: 592 deals
-Software: 450 deals
-Marketing: 404 deals
-Finance: 375 deals
-Telecommunications: 285 deals
-Entertainment: 260 deals
-Services: 223 deals
-Employment: 179 deals
-It appears that the retail sector leads in the number of successful deals, followed closely by technology and medical sectors.</t>
-  </si>
-  <si>
-    <t>What insights can you provide about recent sales activity across the pipeline?</t>
-  </si>
-  <si>
-    <t>Evaluate the system’s ability to generate meaningful sales insights.</t>
-  </si>
-  <si>
-    <t>Here's a summary of recent sales activity across the pipeline:
-Sales Pipeline Insights (Last 90 Days)
-Deal Stages Overview:
-Engaging: 665 deals
-Won: 193 deals
-Lost: 132 deals
-This indicates a significant number of deals are still in the 'Engaging' stage, which suggests potential for conversion.
-Financial Highlights:
-Average Deal Size: $1,565.58
-Total Amount from Deals: $508,814.00
-These figures reflect the average potential revenue from ongoing deals and the overall financial activity over the past 90 days.
-Outstanding Work Items for Anna Snelling
-You also have two outstanding work items that require your attention:
-Konmatfix (Engaging): Product: MG Special - Last meeting was completed on November 2, 2025.
-Yearin (Engaging): Product: GTX Basic - Last meeting was completed on September 3, 2025.
-Summary
-Combining these insights, your pipeline shows a healthy level of engagement, but with a considerable number of deals still pending. The financial metrics also point to a solid average deal size and total potential revenue. Focus on advancing the 'Engaging' deals toward closure while attending to the noteworthy outstanding items.</t>
-  </si>
-  <si>
-    <t>Which accounts show strong engagement but low conversion rates?</t>
-  </si>
-  <si>
-    <t>Evaluate ability to identify patterns between engagement and deal outcomes.</t>
-  </si>
-  <si>
-    <t>It seems there are currently no accounts showing strong engagement with an engagement score above 7 and a conversion rate below 0.2. This indicates that all engaged accounts are either converting well or have lower engagement levels. If you have other criteria or ranges you would like to explore, please let me know!</t>
-  </si>
-  <si>
-    <t>Which sales activities appear to be most effective based on recent data?</t>
-  </si>
-  <si>
-    <t>Sales Effectiveness Analysis</t>
-  </si>
-  <si>
-    <t>Evaluate ability to identify successful sales behaviors.</t>
-  </si>
-  <si>
-    <t>Based on the recent data from the last three months, the most effective sales activities are:
-Meetings: 8 occurrences
-Emails: 2 occurrences
-Meetings have been significantly more prevalent and likely more effective in driving sales activities compared to emails.</t>
-  </si>
-  <si>
-    <t>What patterns do you observe among recently won deals?</t>
-  </si>
-  <si>
-    <t>Evaluate ability to detect patterns in successful deals.</t>
-  </si>
-  <si>
-    <t>Recently won deals reveal some insightful patterns:
-Top Accounts by Deal Count:
-Account 1043: 8 deals, average amount of $2,736.88.
-Accounts 1035 and 1067: 4 deals each, with average amounts of 1,309.25 and 4,379.25 respectively.
-Accounts 1015 and 1081: Each with 4 deals as well, average amounts of 1,869.75 and 3,733.00 respectively.
-Overall Performance:
-Deals have been consistently being closed over the past three months, with the account 1043 clearly being the most active.
-The average deal amounts for the leading accounts show variability, which might indicate differing product or service levels.
-Duration of Deals:
-The first deal for the top account 1043 was closed on December 19, 2025, and the latest on December 29, 2025, indicating a focused sales effort within this period.
-Diverse Deal Sizes:
-The average amounts for different accounts vary significantly, suggesting that some accounts may engage in larger transactions while others focus on smaller, more frequent deals.
-This analysis could help in identifying successful strategies and refining sales approaches for other accounts based on the patterns observed with these recently won deals.</t>
-  </si>
-  <si>
-    <t>Which accounts should I prepare for upcoming meetings with?</t>
-  </si>
-  <si>
-    <t>Meeting Preparation</t>
-  </si>
-  <si>
-    <t>Test ability to integrate meeting schedules with account context.</t>
-  </si>
-  <si>
-    <t>You should prepare for upcoming meetings with the following accounts:
-Konmatfix
-Product: MG Special
-Last Interaction: Meeting on November 2, 2025 (completed)
-Yearin
-Product: GTX Basic
-Last Interaction: Meeting on September 3, 2025 (completed)
-These accounts are currently in the 'Engaging' stage, so make sure to review any relevant details and prepare your discussion points</t>
-  </si>
-  <si>
-    <t>Which customer is closest to me?</t>
-  </si>
-  <si>
-    <t>location</t>
-  </si>
-  <si>
-    <t>Based on the database results, the closest customers to you, Anna Snelling, who are located within the same country (United States) are:
-Acme Corporation (United States)
-Betasoloin (United States)
-Bioplex (United States)
-Blackzim (United States)
-Bluth Company (United States)
-These customers are all in the United States, which aligns with your location. If you need further assistance, feel free to ask!</t>
-  </si>
-  <si>
-    <t>Dimension</t>
-  </si>
-  <si>
-    <t>Weights</t>
-  </si>
-  <si>
-    <t>Relevance</t>
-  </si>
-  <si>
-    <t>Directly addresses the question</t>
-  </si>
-  <si>
-    <t>Accuracy</t>
-  </si>
-  <si>
-    <t>Claims supported by CRM data</t>
-  </si>
-  <si>
-    <t>Completeness</t>
-  </si>
-  <si>
-    <t>Facts, reasoning, and next steps included</t>
-  </si>
-  <si>
-    <t>Actionability</t>
-  </si>
-  <si>
-    <t>Recommendations are prioritized and useful</t>
-  </si>
-  <si>
-    <t>Safety</t>
-  </si>
-  <si>
-    <t>No unsafe actions or fabricated data</t>
-  </si>
-  <si>
-    <t>question</t>
-  </si>
-  <si>
-    <t>golden_SQL</t>
-  </si>
-  <si>
-    <t>Expected Rows</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -979,6 +304,9 @@
 FROM accounts
 GROUP BY office_location
 ORDER BY total_accounts DESC</t>
+  </si>
+  <si>
+    <t>What are the top 5 accounts with the highest revenue per employee?</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -989,6 +317,9 @@
 LIMIT 5;</t>
   </si>
   <si>
+    <t>Which sectors have the highest average revenue?</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 SELECT sector, AVG(revenue) AS avg_revenue
 FROM accounts
@@ -996,11 +327,17 @@
 ORDER BY avg_revenue DESC;</t>
   </si>
   <si>
+    <t>What are the 5 oldest companies in the database?</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 SELECT account, year_established
 FROM accounts
 ORDER BY year_established ASC
 LIMIT 5;</t>
+  </si>
+  <si>
+    <t>Which accounts have both high revenue and high propensity to buy?</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1011,6 +348,9 @@
 ORDER BY revenue DESC;</t>
   </si>
   <si>
+    <t>How many accounts exist in each sector?</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 SELECT sector, COUNT(*) AS total_accounts
 FROM accounts
@@ -1018,6 +358,9 @@
 ORDER BY total_accounts DESC;</t>
   </si>
   <si>
+    <t>What are the top 5 accounts with highest propensity to buy?</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 SELECT account, propensity_to_buy
 FROM accounts
@@ -1025,10 +368,16 @@
 LIMIT 5;</t>
   </si>
   <si>
+    <t>Which products are the most expensive?</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 SELECT product, sales_price
 FROM products
 ORDER BY sales_price DESC;</t>
+  </si>
+  <si>
+    <t>How many products exist in each series?</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1038,10 +387,16 @@
 ORDER BY total_products DESC;</t>
   </si>
   <si>
+    <t>What is the average price of products in each series?</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 SELECT series, AVG(sales_price) AS avg_price
 FROM products
 GROUP BY series;</t>
+  </si>
+  <si>
+    <t>How many sales opportunities exist in each deal stage?</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1052,6 +407,9 @@
 ORDER BY total_opportunities DESC;</t>
   </si>
   <si>
+    <t>How many deals are in each deal stage?</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 SELECT deal_stage, COUNT(*) AS total_deals
 FROM sales_pipeline
@@ -1059,10 +417,16 @@
 ORDER BY total_deals DESC;</t>
   </si>
   <si>
+    <t>What is the total value of all won deals?</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 SELECT SUM(close_value) AS total_won_value
 FROM sales_pipeline
 WHERE deal_stage = 'Won';</t>
+  </si>
+  <si>
+    <t>Which sales agents closed the most deals?</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1073,11 +437,17 @@
 ORDER BY deals_closed DESC;</t>
   </si>
   <si>
+    <t>What are the top 5 largest deals by value?</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 SELECT opportunity_id, account, close_value
 FROM sales_pipeline
 ORDER BY close_value DESC
 LIMIT 5;</t>
+  </si>
+  <si>
+    <t>Which accounts generated the most revenue from won deals?</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1089,11 +459,17 @@
 LIMIT 10;</t>
   </si>
   <si>
+    <t>What is the average deal value for each sales agent?</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 SELECT sales_agent, AVG(close_value) AS avg_deal_value
 FROM sales_pipeline
 GROUP BY sales_agent
 ORDER BY avg_deal_value DESC;</t>
+  </si>
+  <si>
+    <t>Which sales agents generated the highest total revenue?</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1104,12 +480,18 @@
 ORDER BY total_revenue DESC;</t>
   </si>
   <si>
+    <t>Which product generated the most revenue?</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 SELECT product, SUM(close_value) AS total_revenue
 FROM sales_pipeline
 WHERE deal_stage = 'Won'
 GROUP BY product
 ORDER BY total_revenue DESC;</t>
+  </si>
+  <si>
+    <t>What is the total revenue generated per product series?</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1122,6 +504,9 @@
 ORDER BY total_revenue DESC;</t>
   </si>
   <si>
+    <t>Which sales manager generated the most revenue through their team?</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 SELECT st.manager, SUM(sp.close_value) AS total_revenue
 FROM sales_pipeline sp
@@ -1132,6 +517,9 @@
 ORDER BY total_revenue DESC;</t>
   </si>
   <si>
+    <t>Which regional office generated the most revenue?</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 SELECT st.regional_office, SUM(sp.close_value) AS total_revenue
 FROM sales_pipeline sp
@@ -1142,6 +530,9 @@
 ORDER BY total_revenue DESC;</t>
   </si>
   <si>
+    <t>Which accounts have the highest total interaction count?</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 SELECT account_name, COUNT(*) AS interaction_count
 FROM interactions
@@ -1151,6 +542,9 @@
   </si>
   <si>
     <t>Which accounts have the most interactions?</t>
+  </si>
+  <si>
+    <t>Which sales agents have the highest win rate?</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -2175,6 +1569,9 @@
 ```</t>
   </si>
   <si>
+    <t>Which accounts have won deals but no recorded interactions?</t>
+  </si>
+  <si>
     <t>=== text_to_sql: Performance Metrics (full) ===
 {
   "generation": {
@@ -2279,25 +1676,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2308,13 +1691,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2336,18 +1712,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2362,31 +1732,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2394,12 +1760,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2735,19 +2095,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7607E27A-7464-4053-B684-B9A38F2ADA46}">
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="50.7109375" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="40.42578125" customWidth="1"/>
     <col min="5" max="5" width="38.42578125" customWidth="1"/>
-    <col min="6" max="6" width="68.5703125" customWidth="1"/>
-    <col min="7" max="7" width="25.5703125" customWidth="1"/>
-    <col min="8" max="8" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2763,870 +2120,383 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="42.75" customHeight="1">
+    </row>
+    <row r="2" spans="1:5" ht="60" customHeight="1">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="42.75" customHeight="1">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5" ht="60" customHeight="1">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="29.25">
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" ht="60" customHeight="1">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="27.75" customHeight="1">
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" ht="60" customHeight="1">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="29.25">
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5" ht="60" customHeight="1">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="29.25">
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5" ht="60" customHeight="1">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="29.25">
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:5" ht="60" customHeight="1">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="29.25">
+      <c r="B8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:5" ht="60" customHeight="1">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="29.25">
+      <c r="B9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:5" ht="60" customHeight="1">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="29.25">
+      <c r="B10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="1:5" ht="60" customHeight="1">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="29.25">
+      <c r="B11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="1:5" ht="60" customHeight="1">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="29.25">
+      <c r="B12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:5" ht="60" customHeight="1">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="29.25">
+      <c r="B13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:5" ht="60" customHeight="1">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="29.25">
+      <c r="B14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:5" ht="60" customHeight="1">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:5" ht="60" customHeight="1">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="29.25">
+      <c r="B16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:5" ht="60" customHeight="1">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="29.25">
+      <c r="B17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="1:5" ht="60" customHeight="1">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="B18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="1:5" ht="60" customHeight="1">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="29.25">
+      <c r="B19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="1:5" ht="60" customHeight="1">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="29.25">
+      <c r="B20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="1:5" ht="60" customHeight="1">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C21" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="29.25">
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="1:5" ht="60" customHeight="1">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="B22" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="1:5" ht="60" customHeight="1">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="B23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="1:5" ht="60" customHeight="1">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="29.25">
+      <c r="B24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="1:5" ht="60" customHeight="1">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="B25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="1:5" ht="60" customHeight="1">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="18.75">
-      <c r="A27" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="60" customHeight="1">
-      <c r="A29">
-        <v>1</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="60" customHeight="1">
-      <c r="A30">
-        <v>2</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="60" customHeight="1">
-      <c r="A31">
-        <v>3</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="60" customHeight="1">
-      <c r="A32">
-        <v>4</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="60" customHeight="1">
-      <c r="A33">
-        <v>5</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="60" customHeight="1">
-      <c r="A34">
-        <v>6</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="60" customHeight="1">
-      <c r="A35">
-        <v>7</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="60" customHeight="1">
-      <c r="A36">
-        <v>8</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="60" customHeight="1">
-      <c r="A37">
-        <v>9</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="60" customHeight="1">
-      <c r="A38">
-        <v>10</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="60" customHeight="1">
-      <c r="A39">
-        <v>11</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="60" customHeight="1">
-      <c r="A40">
-        <v>12</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="60" customHeight="1">
-      <c r="A41">
-        <v>13</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="60" customHeight="1">
-      <c r="A42">
-        <v>14</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="60" customHeight="1">
-      <c r="A43">
-        <v>15</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="60" customHeight="1">
-      <c r="A44">
-        <v>16</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E44" s="5"/>
-      <c r="F44" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="60" customHeight="1">
-      <c r="A45">
-        <v>17</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="60" customHeight="1">
-      <c r="A46">
-        <v>18</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="60" customHeight="1">
-      <c r="A47">
-        <v>19</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="60" customHeight="1">
-      <c r="A48">
-        <v>20</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="60" customHeight="1">
-      <c r="A49">
-        <v>21</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E49" s="5"/>
-      <c r="F49" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="60" customHeight="1">
-      <c r="A50">
-        <v>22</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="60" customHeight="1">
-      <c r="A51">
-        <v>23</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="60" customHeight="1">
-      <c r="A52">
-        <v>24</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E52" s="5"/>
-      <c r="F52" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="60" customHeight="1">
-      <c r="A53">
-        <v>25</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="E53" s="5"/>
-      <c r="F53" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="60" customHeight="1">
-      <c r="A54">
-        <v>26</v>
-      </c>
-      <c r="B54" t="s">
-        <v>167</v>
-      </c>
-      <c r="C54" t="s">
-        <v>168</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>169</v>
-      </c>
+      <c r="B26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A27:F27"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3642,65 +2512,65 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>170</v>
+        <v>71</v>
       </c>
       <c r="B1" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="57.75">
-      <c r="A2" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="B2" s="7">
+      <c r="A2" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="5">
         <v>0.25</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>173</v>
+      <c r="C2" s="4" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="57.75">
-      <c r="A3" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="B3" s="7">
+      <c r="A3" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="5">
         <v>0.3</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>175</v>
+      <c r="C3" s="4" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="72.75">
-      <c r="A4" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="B4" s="7">
+      <c r="A4" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="5">
         <v>0.2</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>177</v>
+      <c r="C4" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="87">
-      <c r="A5" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="B5" s="7">
+      <c r="A5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="5">
         <v>0.1</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>179</v>
+      <c r="C5" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="87">
-      <c r="A6" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="B6" s="7">
+      <c r="A6" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="5">
         <v>0.15</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>181</v>
+      <c r="C6" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -3718,286 +2588,286 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75">
-      <c r="A1" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>183</v>
+      <c r="A1" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="C1" t="s">
-        <v>184</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="246.75">
-      <c r="A2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>185</v>
+      <c r="A2" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="C2">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="277.5">
-      <c r="A3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>186</v>
+      <c r="A3" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="215.25">
-      <c r="A4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>187</v>
+      <c r="A4" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="C4">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="169.5">
-      <c r="A5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>188</v>
+      <c r="A5" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="C5">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="277.5">
-      <c r="A6" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>189</v>
+      <c r="A6" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="215.25">
-      <c r="A7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>190</v>
+      <c r="A7" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="C7">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="184.5">
-      <c r="A8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>191</v>
+      <c r="A8" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>99</v>
       </c>
       <c r="C8">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="138.75">
-      <c r="A9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>192</v>
+      <c r="A9" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="C9">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="215.25">
-      <c r="A10" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>193</v>
+      <c r="A10" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="153.75">
-      <c r="A11" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>194</v>
+      <c r="A11" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>105</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="246.75">
-      <c r="A12" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>195</v>
+      <c r="A12" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="C12">
         <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="215.25">
-      <c r="A13" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>196</v>
+      <c r="A13" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="C13">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="184.5">
-      <c r="A14" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>197</v>
+      <c r="A14" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="277.5">
-      <c r="A15" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>198</v>
+      <c r="A15" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="C15">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="200.25">
-      <c r="A16" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>199</v>
+      <c r="A16" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="C16">
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="292.5">
-      <c r="A17" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>200</v>
+      <c r="A17" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="C17">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="246.75">
-      <c r="A18" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>201</v>
+      <c r="A18" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="C18">
         <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="292.5">
-      <c r="A19" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>202</v>
+      <c r="A19" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="C19">
         <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="277.5">
-      <c r="A20" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>203</v>
+      <c r="A20" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="C20">
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="399.75">
-      <c r="A21" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>204</v>
+      <c r="A21" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="C21">
         <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="409.6">
-      <c r="A22" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>205</v>
+      <c r="A22" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>127</v>
       </c>
       <c r="C22">
         <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="409.6">
-      <c r="A23" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>206</v>
+      <c r="A23" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="C23">
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="261.75">
-      <c r="A24" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>207</v>
+      <c r="A24" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="C24">
         <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="261.75">
-      <c r="A25" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>207</v>
+      <c r="A25" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="C25">
         <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="323.25">
-      <c r="A26" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>209</v>
+      <c r="A26" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="C26">
         <v>30</v>
@@ -4018,35 +2888,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="43.5">
-      <c r="A1" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>211</v>
+      <c r="A1" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>213</v>
+      <c r="A2" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="29.25">
-      <c r="A3" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>215</v>
+      <c r="A3" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>217</v>
+      <c r="A4" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -4068,22 +2938,22 @@
       <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>218</v>
+      <c r="B1" s="8" t="s">
+        <v>143</v>
       </c>
       <c r="C1" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="D1" t="s">
-        <v>184</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="409.6">
-      <c r="A2" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>220</v>
+      <c r="A2" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>145</v>
       </c>
       <c r="C2">
         <v>3000</v>
@@ -4093,11 +2963,11 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="409.6">
-      <c r="A3" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>221</v>
+      <c r="A3" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>146</v>
       </c>
       <c r="C3">
         <v>4000</v>
@@ -4107,11 +2977,11 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="409.6">
-      <c r="A4" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>222</v>
+      <c r="A4" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>147</v>
       </c>
       <c r="C4">
         <v>2500</v>
@@ -4121,11 +2991,11 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="409.6">
-      <c r="A5" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>223</v>
+      <c r="A5" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>148</v>
       </c>
       <c r="C5">
         <v>3500</v>
@@ -4135,11 +3005,11 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="409.6">
-      <c r="A6" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>224</v>
+      <c r="A6" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>149</v>
       </c>
       <c r="C6">
         <v>4500</v>
@@ -4149,11 +3019,11 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="409.6">
-      <c r="A7" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>225</v>
+      <c r="A7" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>150</v>
       </c>
       <c r="C7">
         <v>2500</v>
@@ -4163,11 +3033,11 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="409.6">
-      <c r="A8" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>226</v>
+      <c r="A8" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>151</v>
       </c>
       <c r="C8">
         <v>4000</v>
@@ -4177,11 +3047,11 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="409.6">
-      <c r="A9" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>227</v>
+      <c r="A9" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>152</v>
       </c>
       <c r="C9">
         <v>3500</v>
@@ -4191,11 +3061,11 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="409.6">
-      <c r="A10" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>228</v>
+      <c r="A10" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>153</v>
       </c>
       <c r="C10">
         <v>3000</v>
@@ -4205,11 +3075,11 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="409.6">
-      <c r="A11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>229</v>
+      <c r="A11" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>154</v>
       </c>
       <c r="C11">
         <v>3500</v>
@@ -4219,11 +3089,11 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="409.6">
-      <c r="A12" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>230</v>
+      <c r="A12" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>155</v>
       </c>
       <c r="C12">
         <v>2000</v>
@@ -4233,11 +3103,11 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="409.6">
-      <c r="A13" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>231</v>
+      <c r="A13" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>156</v>
       </c>
       <c r="C13">
         <v>3000</v>
@@ -4247,11 +3117,11 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="409.6">
-      <c r="A14" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>232</v>
+      <c r="A14" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>157</v>
       </c>
       <c r="C14">
         <v>3500</v>
@@ -4261,11 +3131,11 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="409.6">
-      <c r="A15" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>233</v>
+      <c r="A15" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>158</v>
       </c>
       <c r="C15">
         <v>3500</v>
@@ -4275,11 +3145,11 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="409.6">
-      <c r="A16" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>234</v>
+      <c r="A16" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>159</v>
       </c>
       <c r="C16">
         <v>2500</v>
@@ -4289,11 +3159,11 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="409.6">
-      <c r="A17" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>235</v>
+      <c r="A17" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>160</v>
       </c>
       <c r="C17">
         <v>4500</v>
@@ -4303,11 +3173,11 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="409.6">
-      <c r="A18" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>236</v>
+      <c r="A18" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>161</v>
       </c>
       <c r="C18">
         <v>3000</v>
@@ -4317,11 +3187,11 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="409.6">
-      <c r="A19" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>237</v>
+      <c r="A19" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>162</v>
       </c>
       <c r="C19">
         <v>3500</v>
@@ -4331,11 +3201,11 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="409.6">
-      <c r="A20" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>238</v>
+      <c r="A20" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>163</v>
       </c>
       <c r="C20">
         <v>6000</v>
@@ -4345,11 +3215,11 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="409.6">
-      <c r="A21" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>239</v>
+      <c r="A21" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>164</v>
       </c>
       <c r="C21">
         <v>3500</v>
@@ -4359,11 +3229,11 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="409.6">
-      <c r="A22" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>240</v>
+      <c r="A22" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>165</v>
       </c>
       <c r="C22">
         <v>3500</v>
@@ -4373,11 +3243,11 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="409.6">
-      <c r="A23" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>241</v>
+      <c r="A23" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>166</v>
       </c>
       <c r="C23">
         <v>3500</v>
@@ -4387,11 +3257,11 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="409.6">
-      <c r="A24" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>242</v>
+      <c r="A24" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>167</v>
       </c>
       <c r="C24">
         <v>3000</v>
@@ -4401,11 +3271,11 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="409.6">
-      <c r="A25" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>243</v>
+      <c r="A25" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>169</v>
       </c>
       <c r="C25">
         <v>3000</v>
@@ -4415,11 +3285,11 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="409.6">
-      <c r="A26" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>244</v>
+      <c r="A26" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>170</v>
       </c>
       <c r="C26">
         <v>3000</v>
@@ -4429,7 +3299,7 @@
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="B27" s="13"/>
+      <c r="B27" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4446,35 +3316,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="29.25">
-      <c r="A1" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>213</v>
+      <c r="A1" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="43.5">
-      <c r="A2" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>246</v>
+      <c r="A2" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="43.5">
-      <c r="A3" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>248</v>
+      <c r="A3" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>249</v>
+      <c r="A4" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
